--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6502.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6502.xlsx
@@ -2154,6 +2154,12 @@
       <c r="C29" t="n">
         <v>1.7</v>
       </c>
+      <c r="D29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.25</v>
+      </c>
       <c r="F29" t="n">
         <v>1.312</v>
       </c>
@@ -2176,17 +2182,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, M2@DRIVE, M6@DRIVE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, M2@DRIVE, M6@DRIVE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, Y@HEX, M14@DRIVE, C3HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6502-16-12-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, M2@DRIVE=M2, M6@DRIVE=M6, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6502-16-12-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, M2@DRIVE=M2, M6@DRIVE=M6, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, Y@HEX=Y, M14@DRIVE=M, C3HEX@HEX=C; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
